--- a/附件包/Vector.xlsx
+++ b/附件包/Vector.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\KratosAI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\KratosAI\附件包\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AB90314-1B39-401C-B6BD-FDE90CC2C5FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6370815F-6EFD-4993-8D09-AA9BBE77FB1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="281">
   <si>
     <t>标签名 (Vector.xxx)</t>
   </si>
@@ -656,30 +656,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F4E79"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Freeze</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F4E79"/>
-        <rFont val="宋体"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>模式</t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">AE </t>
     </r>
     <r>
@@ -2614,12 +2590,62 @@
     </r>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F4E79"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Freeze</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F4E79"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>模式</t>
+    </r>
+  </si>
+  <si>
+    <t>Vector.SubjectToCliffs</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Vector</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+      </rPr>
+      <t>存在期间禁止抛射体因为撞高地而爆炸。默认</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>不会撞山。</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2788,8 +2814,14 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2804,12 +2836,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD6E4F0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -2888,7 +2914,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2997,73 +3023,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
@@ -3085,6 +3044,48 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3092,6 +3093,35 @@
     <xf numFmtId="0" fontId="17" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -3418,16 +3448,16 @@
       </c>
     </row>
     <row r="2" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="69" t="s">
+      <c r="A2" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="70"/>
-      <c r="C2" s="70"/>
-      <c r="D2" s="71"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="46"/>
     </row>
     <row r="3" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="19" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B3" s="20" t="s">
         <v>5</v>
@@ -3441,7 +3471,7 @@
     </row>
     <row r="4" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="19" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B4" s="20" t="s">
         <v>5</v>
@@ -3450,12 +3480,12 @@
         <v>8</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B5" s="20" t="s">
         <v>9</v>
@@ -3464,12 +3494,12 @@
         <v>10</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="19" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B6" s="20" t="s">
         <v>9</v>
@@ -3483,7 +3513,7 @@
     </row>
     <row r="7" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="19" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B7" s="20" t="s">
         <v>9</v>
@@ -3497,7 +3527,7 @@
     </row>
     <row r="8" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="19" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B8" s="20" t="s">
         <v>13</v>
@@ -3506,12 +3536,12 @@
         <v>14</v>
       </c>
       <c r="D8" s="29" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B9" s="20" t="s">
         <v>15</v>
@@ -3520,12 +3550,12 @@
         <v>16</v>
       </c>
       <c r="D9" s="29" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="19" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B10" s="20" t="s">
         <v>9</v>
@@ -3539,7 +3569,7 @@
     </row>
     <row r="11" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="19" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B11" s="20" t="s">
         <v>9</v>
@@ -3553,7 +3583,7 @@
     </row>
     <row r="12" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="19" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B12" s="20" t="s">
         <v>9</v>
@@ -3567,7 +3597,7 @@
     </row>
     <row r="13" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="19" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B13" s="20" t="s">
         <v>5</v>
@@ -3576,62 +3606,70 @@
         <v>109</v>
       </c>
       <c r="D13" s="39" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" s="44" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="51" t="s">
         <v>272</v>
       </c>
-      <c r="B14" s="52" t="s">
+    </row>
+    <row r="14" spans="1:4" s="76" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="73" t="s">
+        <v>271</v>
+      </c>
+      <c r="B14" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="52" t="s">
-        <v>255</v>
-      </c>
-      <c r="D14" s="54" t="s">
-        <v>277</v>
+      <c r="C14" s="74" t="s">
+        <v>254</v>
+      </c>
+      <c r="D14" s="75" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="15" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="72" t="s">
-        <v>123</v>
-      </c>
-      <c r="B15" s="73"/>
-      <c r="C15" s="73"/>
-      <c r="D15" s="74"/>
-    </row>
-    <row r="16" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="B16" s="17" t="s">
+      <c r="A15" s="70" t="s">
+        <v>279</v>
+      </c>
+      <c r="B15" s="71" t="s">
+        <v>112</v>
+      </c>
+      <c r="C15" s="71" t="s">
+        <v>113</v>
+      </c>
+      <c r="D15" s="72" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="47" t="s">
+        <v>278</v>
+      </c>
+      <c r="B16" s="48"/>
+      <c r="C16" s="48"/>
+      <c r="D16" s="49"/>
+    </row>
+    <row r="17" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="B17" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="C16" s="17" t="s">
+      <c r="C17" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D17" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="11"/>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-    </row>
     <row r="18" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="75" t="s">
+      <c r="A18" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="76"/>
-      <c r="C18" s="76"/>
-      <c r="D18" s="77"/>
+      <c r="B18" s="51"/>
+      <c r="C18" s="51"/>
+      <c r="D18" s="52"/>
     </row>
     <row r="19" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B19" s="17" t="s">
         <v>15</v>
@@ -3645,7 +3683,7 @@
     </row>
     <row r="20" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B20" s="17" t="s">
         <v>15</v>
@@ -3659,7 +3697,7 @@
     </row>
     <row r="21" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B21" s="17" t="s">
         <v>25</v>
@@ -3668,7 +3706,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="18" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="22" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
@@ -3678,16 +3716,16 @@
       <c r="D22" s="11"/>
     </row>
     <row r="23" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="60" t="s">
+      <c r="A23" s="53" t="s">
         <v>118</v>
       </c>
-      <c r="B23" s="61"/>
-      <c r="C23" s="61"/>
-      <c r="D23" s="62"/>
+      <c r="B23" s="54"/>
+      <c r="C23" s="54"/>
+      <c r="D23" s="55"/>
     </row>
     <row r="24" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="31" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B24" s="20" t="s">
         <v>5</v>
@@ -3701,7 +3739,7 @@
     </row>
     <row r="25" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="31" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B25" s="20" t="s">
         <v>49</v>
@@ -3715,7 +3753,7 @@
     </row>
     <row r="26" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="31" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B26" s="20" t="s">
         <v>5</v>
@@ -3729,7 +3767,7 @@
     </row>
     <row r="27" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="31" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B27" s="20" t="s">
         <v>5</v>
@@ -3743,7 +3781,7 @@
     </row>
     <row r="28" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="33" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B28" s="20" t="s">
         <v>5</v>
@@ -3757,7 +3795,7 @@
     </row>
     <row r="29" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="31" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B29" s="20" t="s">
         <v>9</v>
@@ -3770,16 +3808,16 @@
       </c>
     </row>
     <row r="30" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="63" t="s">
+      <c r="A30" s="56" t="s">
         <v>98</v>
       </c>
-      <c r="B30" s="61"/>
-      <c r="C30" s="61"/>
-      <c r="D30" s="62"/>
+      <c r="B30" s="54"/>
+      <c r="C30" s="54"/>
+      <c r="D30" s="55"/>
     </row>
     <row r="31" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="33" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B31" s="20" t="s">
         <v>9</v>
@@ -3793,7 +3831,7 @@
     </row>
     <row r="32" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="33" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B32" s="20" t="s">
         <v>5</v>
@@ -3806,16 +3844,16 @@
       </c>
     </row>
     <row r="33" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="60" t="s">
+      <c r="A33" s="53" t="s">
         <v>119</v>
       </c>
-      <c r="B33" s="61"/>
-      <c r="C33" s="61"/>
-      <c r="D33" s="62"/>
+      <c r="B33" s="54"/>
+      <c r="C33" s="54"/>
+      <c r="D33" s="55"/>
     </row>
     <row r="34" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="35" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B34" s="20" t="s">
         <v>15</v>
@@ -3829,7 +3867,7 @@
     </row>
     <row r="35" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="35" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B35" s="20" t="s">
         <v>49</v>
@@ -3843,7 +3881,7 @@
     </row>
     <row r="36" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="33" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B36" s="20" t="s">
         <v>49</v>
@@ -3857,7 +3895,7 @@
     </row>
     <row r="37" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="33" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B37" s="20" t="s">
         <v>49</v>
@@ -3871,7 +3909,7 @@
     </row>
     <row r="38" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="33" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B38" s="20" t="s">
         <v>29</v>
@@ -3885,7 +3923,7 @@
     </row>
     <row r="39" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="33" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B39" s="20" t="s">
         <v>29</v>
@@ -3899,7 +3937,7 @@
     </row>
     <row r="40" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="33" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B40" s="20" t="s">
         <v>29</v>
@@ -3913,7 +3951,7 @@
     </row>
     <row r="41" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="33" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B41" s="20" t="s">
         <v>49</v>
@@ -3927,7 +3965,7 @@
     </row>
     <row r="42" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="33" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B42" s="20" t="s">
         <v>29</v>
@@ -3939,23 +3977,23 @@
         <v>115</v>
       </c>
     </row>
-    <row r="43" spans="1:4" s="44" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="44" t="s">
+    <row r="43" spans="1:4" s="76" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="76" t="s">
+        <v>265</v>
+      </c>
+      <c r="B43" s="71" t="s">
         <v>266</v>
       </c>
-      <c r="B43" s="45" t="s">
+      <c r="C43" s="71" t="s">
         <v>267</v>
       </c>
-      <c r="C43" s="45" t="s">
-        <v>268</v>
-      </c>
-      <c r="D43" s="46" t="s">
-        <v>274</v>
+      <c r="D43" s="77" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="44" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="40" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B44" s="37" t="s">
         <v>9</v>
@@ -3964,12 +4002,12 @@
         <v>10</v>
       </c>
       <c r="D44" s="42" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="45" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="40" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B45" s="37" t="s">
         <v>29</v>
@@ -3978,12 +4016,12 @@
         <v>30</v>
       </c>
       <c r="D45" s="42" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="46" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="40" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B46" s="37" t="s">
         <v>5</v>
@@ -3997,7 +4035,7 @@
     </row>
     <row r="47" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="40" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B47" s="37" t="s">
         <v>25</v>
@@ -4011,7 +4049,7 @@
     </row>
     <row r="48" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="40" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B48" s="37" t="s">
         <v>51</v>
@@ -4025,7 +4063,7 @@
     </row>
     <row r="49" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="41" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B49" s="37" t="s">
         <v>49</v>
@@ -4039,7 +4077,7 @@
     </row>
     <row r="50" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="41" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B50" s="37" t="s">
         <v>25</v>
@@ -4048,12 +4086,12 @@
         <v>8</v>
       </c>
       <c r="D50" s="39" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="51" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="34" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B51" s="20" t="s">
         <v>51</v>
@@ -4066,16 +4104,16 @@
       </c>
     </row>
     <row r="52" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="63" t="s">
+      <c r="A52" s="56" t="s">
         <v>37</v>
       </c>
-      <c r="B52" s="61"/>
-      <c r="C52" s="61"/>
-      <c r="D52" s="62"/>
+      <c r="B52" s="54"/>
+      <c r="C52" s="54"/>
+      <c r="D52" s="55"/>
     </row>
     <row r="53" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="19" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B53" s="20" t="s">
         <v>5</v>
@@ -4089,7 +4127,7 @@
     </row>
     <row r="54" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="19" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B54" s="20" t="s">
         <v>5</v>
@@ -4103,7 +4141,7 @@
     </row>
     <row r="55" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="19" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B55" s="20" t="s">
         <v>5</v>
@@ -4117,7 +4155,7 @@
     </row>
     <row r="56" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="19" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B56" s="20" t="s">
         <v>5</v>
@@ -4131,7 +4169,7 @@
     </row>
     <row r="57" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="19" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B57" s="20" t="s">
         <v>5</v>
@@ -4145,7 +4183,7 @@
     </row>
     <row r="58" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="19" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B58" s="20" t="s">
         <v>25</v>
@@ -4159,7 +4197,7 @@
     </row>
     <row r="59" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="19" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B59" s="20" t="s">
         <v>25</v>
@@ -4173,7 +4211,7 @@
     </row>
     <row r="60" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="19" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B60" s="20" t="s">
         <v>25</v>
@@ -4187,7 +4225,7 @@
     </row>
     <row r="61" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="19" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B61" s="20" t="s">
         <v>25</v>
@@ -4201,7 +4239,7 @@
     </row>
     <row r="62" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B62" s="20" t="s">
         <v>15</v>
@@ -4215,7 +4253,7 @@
     </row>
     <row r="63" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="19" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B63" s="20" t="s">
         <v>9</v>
@@ -4224,12 +4262,12 @@
         <v>10</v>
       </c>
       <c r="D63" s="24" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="64" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="19" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B64" s="20" t="s">
         <v>49</v>
@@ -4243,7 +4281,7 @@
     </row>
     <row r="65" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="19" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B65" s="20" t="s">
         <v>51</v>
@@ -4257,7 +4295,7 @@
     </row>
     <row r="66" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="19" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B66" s="20" t="s">
         <v>29</v>
@@ -4271,7 +4309,7 @@
     </row>
     <row r="67" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="19" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B67" s="20" t="s">
         <v>5</v>
@@ -4285,7 +4323,7 @@
     </row>
     <row r="68" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="19" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B68" s="20" t="s">
         <v>5</v>
@@ -4299,7 +4337,7 @@
     </row>
     <row r="69" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="19" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B69" s="20" t="s">
         <v>5</v>
@@ -4313,7 +4351,7 @@
     </row>
     <row r="70" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="19" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B70" s="20" t="s">
         <v>9</v>
@@ -4327,7 +4365,7 @@
     </row>
     <row r="71" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="19" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B71" s="20" t="s">
         <v>9</v>
@@ -4341,7 +4379,7 @@
     </row>
     <row r="72" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="19" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B72" s="20" t="s">
         <v>9</v>
@@ -4350,34 +4388,34 @@
         <v>10</v>
       </c>
       <c r="D72" s="24" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="73" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="25" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B73" s="26" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C73" s="27">
         <v>0</v>
       </c>
       <c r="D73" s="28" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="74" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="60" t="s">
-        <v>134</v>
-      </c>
-      <c r="B74" s="61"/>
-      <c r="C74" s="61"/>
-      <c r="D74" s="62"/>
+      <c r="A74" s="53" t="s">
+        <v>133</v>
+      </c>
+      <c r="B74" s="54"/>
+      <c r="C74" s="54"/>
+      <c r="D74" s="55"/>
     </row>
     <row r="75" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="19" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B75" s="20" t="s">
         <v>15</v>
@@ -4386,12 +4424,12 @@
         <v>16</v>
       </c>
       <c r="D75" s="29" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="76" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="19" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B76" s="20" t="s">
         <v>15</v>
@@ -4405,7 +4443,7 @@
     </row>
     <row r="77" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="19" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B77" s="20" t="s">
         <v>15</v>
@@ -4419,7 +4457,7 @@
     </row>
     <row r="78" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="19" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B78" s="20" t="s">
         <v>15</v>
@@ -4433,7 +4471,7 @@
     </row>
     <row r="79" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="19" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B79" s="20" t="s">
         <v>25</v>
@@ -4447,7 +4485,7 @@
     </row>
     <row r="80" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="19" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B80" s="20" t="s">
         <v>25</v>
@@ -4461,7 +4499,7 @@
     </row>
     <row r="81" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="19" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B81" s="20" t="s">
         <v>25</v>
@@ -4475,7 +4513,7 @@
     </row>
     <row r="82" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="19" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B82" s="20" t="s">
         <v>29</v>
@@ -4489,7 +4527,7 @@
     </row>
     <row r="83" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="19" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B83" s="20" t="s">
         <v>29</v>
@@ -4503,7 +4541,7 @@
     </row>
     <row r="84" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="19" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B84" s="20" t="s">
         <v>29</v>
@@ -4515,39 +4553,39 @@
         <v>33</v>
       </c>
     </row>
-    <row r="85" spans="1:4" s="44" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="51" t="s">
-        <v>270</v>
-      </c>
-      <c r="B85" s="52" t="s">
+    <row r="85" spans="1:4" s="76" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A85" s="73" t="s">
+        <v>269</v>
+      </c>
+      <c r="B85" s="74" t="s">
         <v>112</v>
       </c>
-      <c r="C85" s="52" t="s">
-        <v>269</v>
-      </c>
-      <c r="D85" s="53" t="s">
-        <v>276</v>
+      <c r="C85" s="74" t="s">
+        <v>268</v>
+      </c>
+      <c r="D85" s="78" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="86" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="64" t="s">
-        <v>129</v>
-      </c>
-      <c r="B86" s="65"/>
-      <c r="C86" s="65"/>
-      <c r="D86" s="66"/>
+      <c r="A86" s="62" t="s">
+        <v>128</v>
+      </c>
+      <c r="B86" s="63"/>
+      <c r="C86" s="63"/>
+      <c r="D86" s="64"/>
     </row>
     <row r="87" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="67" t="s">
+      <c r="A87" s="65" t="s">
         <v>59</v>
       </c>
-      <c r="B87" s="65"/>
-      <c r="C87" s="65"/>
-      <c r="D87" s="66"/>
+      <c r="B87" s="63"/>
+      <c r="C87" s="63"/>
+      <c r="D87" s="64"/>
     </row>
     <row r="88" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="19" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B88" s="20" t="s">
         <v>15</v>
@@ -4561,7 +4599,7 @@
     </row>
     <row r="89" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="19" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B89" s="20" t="s">
         <v>15</v>
@@ -4575,7 +4613,7 @@
     </row>
     <row r="90" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="19" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B90" s="20" t="s">
         <v>25</v>
@@ -4588,16 +4626,16 @@
       </c>
     </row>
     <row r="91" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="68" t="s">
-        <v>246</v>
-      </c>
-      <c r="B91" s="65"/>
-      <c r="C91" s="65"/>
-      <c r="D91" s="66"/>
+      <c r="A91" s="66" t="s">
+        <v>245</v>
+      </c>
+      <c r="B91" s="63"/>
+      <c r="C91" s="63"/>
+      <c r="D91" s="64"/>
     </row>
     <row r="92" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="19" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B92" s="20" t="s">
         <v>15</v>
@@ -4611,7 +4649,7 @@
     </row>
     <row r="93" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="19" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B93" s="20" t="s">
         <v>5</v>
@@ -4625,7 +4663,7 @@
     </row>
     <row r="94" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="19" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B94" s="20" t="s">
         <v>5</v>
@@ -4639,7 +4677,7 @@
     </row>
     <row r="95" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="19" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B95" s="20" t="s">
         <v>5</v>
@@ -4653,7 +4691,7 @@
     </row>
     <row r="96" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="19" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B96" s="20" t="s">
         <v>5</v>
@@ -4667,7 +4705,7 @@
     </row>
     <row r="97" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="19" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B97" s="20" t="s">
         <v>9</v>
@@ -4681,7 +4719,7 @@
     </row>
     <row r="98" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="19" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B98" s="20" t="s">
         <v>9</v>
@@ -4695,7 +4733,7 @@
     </row>
     <row r="99" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="19" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B99" s="20" t="s">
         <v>5</v>
@@ -4709,7 +4747,7 @@
     </row>
     <row r="100" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="19" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B100" s="20" t="s">
         <v>49</v>
@@ -4718,12 +4756,12 @@
         <v>21</v>
       </c>
       <c r="D100" s="29" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="101" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="19" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B101" s="20" t="s">
         <v>49</v>
@@ -4732,12 +4770,12 @@
         <v>21</v>
       </c>
       <c r="D101" s="29" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="102" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="19" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B102" s="20" t="s">
         <v>49</v>
@@ -4746,7 +4784,7 @@
         <v>21</v>
       </c>
       <c r="D102" s="29" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="103" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -4768,16 +4806,16 @@
       <c r="D105" s="3"/>
     </row>
     <row r="106" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="55" t="s">
-        <v>245</v>
-      </c>
-      <c r="B106" s="56"/>
-      <c r="C106" s="56"/>
-      <c r="D106" s="57"/>
+      <c r="A106" s="57" t="s">
+        <v>244</v>
+      </c>
+      <c r="B106" s="58"/>
+      <c r="C106" s="58"/>
+      <c r="D106" s="59"/>
     </row>
     <row r="107" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B107" s="17" t="s">
         <v>5</v>
@@ -4791,7 +4829,7 @@
     </row>
     <row r="108" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B108" s="17" t="s">
         <v>5</v>
@@ -4805,7 +4843,7 @@
     </row>
     <row r="109" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B109" s="17" t="s">
         <v>25</v>
@@ -4819,7 +4857,7 @@
     </row>
     <row r="110" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B110" s="17" t="s">
         <v>49</v>
@@ -4828,26 +4866,26 @@
         <v>21</v>
       </c>
       <c r="D110" s="30" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="111" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B111" s="17" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C111" s="17" t="s">
         <v>21</v>
       </c>
       <c r="D111" s="30" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="112" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B112" s="17" t="s">
         <v>5</v>
@@ -4861,7 +4899,7 @@
     </row>
     <row r="113" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B113" s="17" t="s">
         <v>5</v>
@@ -4875,7 +4913,7 @@
     </row>
     <row r="114" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B114" s="17" t="s">
         <v>5</v>
@@ -4889,7 +4927,7 @@
     </row>
     <row r="115" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B115" s="17" t="s">
         <v>9</v>
@@ -4903,7 +4941,7 @@
     </row>
     <row r="116" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B116" s="17" t="s">
         <v>9</v>
@@ -4917,7 +4955,7 @@
     </row>
     <row r="117" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B117" s="17" t="s">
         <v>9</v>
@@ -4931,7 +4969,7 @@
     </row>
     <row r="118" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B118" s="17" t="s">
         <v>9</v>
@@ -4940,12 +4978,12 @@
         <v>10</v>
       </c>
       <c r="D118" s="18" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="119" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B119" s="17" t="s">
         <v>15</v>
@@ -4959,21 +4997,21 @@
     </row>
     <row r="120" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B120" s="17" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C120" s="17" t="s">
         <v>10</v>
       </c>
       <c r="D120" s="30" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="121" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B121" s="17" t="s">
         <v>13</v>
@@ -4987,7 +5025,7 @@
     </row>
     <row r="122" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B122" s="17" t="s">
         <v>15</v>
@@ -5000,16 +5038,16 @@
       </c>
     </row>
     <row r="123" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="55" t="s">
-        <v>254</v>
-      </c>
-      <c r="B123" s="58"/>
-      <c r="C123" s="58"/>
-      <c r="D123" s="59"/>
+      <c r="A123" s="57" t="s">
+        <v>253</v>
+      </c>
+      <c r="B123" s="60"/>
+      <c r="C123" s="60"/>
+      <c r="D123" s="61"/>
     </row>
     <row r="124" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B124" s="17" t="s">
         <v>15</v>
@@ -5023,7 +5061,7 @@
     </row>
     <row r="125" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B125" s="17" t="s">
         <v>15</v>
@@ -5037,7 +5075,7 @@
     </row>
     <row r="126" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B126" s="17" t="s">
         <v>15</v>
@@ -5051,7 +5089,7 @@
     </row>
     <row r="127" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B127" s="17" t="s">
         <v>15</v>
@@ -5065,7 +5103,7 @@
     </row>
     <row r="128" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B128" s="17" t="s">
         <v>25</v>
@@ -5079,7 +5117,7 @@
     </row>
     <row r="129" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B129" s="17" t="s">
         <v>25</v>
@@ -5093,7 +5131,7 @@
     </row>
     <row r="130" spans="1:4" s="22" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B130" s="17" t="s">
         <v>25</v>
@@ -5105,18 +5143,18 @@
         <v>85</v>
       </c>
     </row>
-    <row r="131" spans="1:4" s="49" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A131" s="47" t="s">
-        <v>271</v>
-      </c>
-      <c r="B131" s="48" t="s">
+    <row r="131" spans="1:4" s="82" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A131" s="79" t="s">
+        <v>270</v>
+      </c>
+      <c r="B131" s="80" t="s">
         <v>9</v>
       </c>
-      <c r="C131" s="48" t="s">
-        <v>269</v>
-      </c>
-      <c r="D131" s="50" t="s">
-        <v>275</v>
+      <c r="C131" s="80" t="s">
+        <v>268</v>
+      </c>
+      <c r="D131" s="81" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.15">
@@ -5125,11 +5163,6 @@
   </sheetData>
   <autoFilter ref="A1:D1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="13">
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="A30:D30"/>
     <mergeCell ref="A106:D106"/>
     <mergeCell ref="A123:D123"/>
     <mergeCell ref="A33:D33"/>
@@ -5138,6 +5171,11 @@
     <mergeCell ref="A87:D87"/>
     <mergeCell ref="A91:D91"/>
     <mergeCell ref="A74:D74"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A16:D16"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5157,16 +5195,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A1" s="63" t="s">
+      <c r="A1" s="56" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="62"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="55"/>
     </row>
     <row r="2" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B2" s="8" t="s">
         <v>15</v>
@@ -5180,7 +5218,7 @@
     </row>
     <row r="3" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A3" s="19" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>15</v>
@@ -5194,7 +5232,7 @@
     </row>
     <row r="4" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A4" s="19" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>25</v>
@@ -5203,7 +5241,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -5227,16 +5265,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="67" t="s">
         <v>118</v>
       </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="71"/>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="46"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A2" s="31" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B2" s="8" t="s">
         <v>5</v>
@@ -5250,7 +5288,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A3" s="31" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>49</v>
@@ -5264,7 +5302,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A4" s="31" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>5</v>
@@ -5278,7 +5316,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A5" s="31" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>5</v>
@@ -5292,7 +5330,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A6" s="33" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>5</v>
@@ -5306,7 +5344,7 @@
     </row>
     <row r="7" spans="1:4" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A7" s="31" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B7" s="8" t="s">
         <v>9</v>
@@ -5319,16 +5357,16 @@
       </c>
     </row>
     <row r="8" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A8" s="69" t="s">
+      <c r="A8" s="44" t="s">
         <v>98</v>
       </c>
-      <c r="B8" s="70"/>
-      <c r="C8" s="70"/>
-      <c r="D8" s="71"/>
+      <c r="B8" s="45"/>
+      <c r="C8" s="45"/>
+      <c r="D8" s="46"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A9" s="33" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B9" s="8" t="s">
         <v>9</v>
@@ -5342,7 +5380,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A10" s="33" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>5</v>
@@ -5355,16 +5393,16 @@
       </c>
     </row>
     <row r="11" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A11" s="78" t="s">
+      <c r="A11" s="67" t="s">
         <v>119</v>
       </c>
-      <c r="B11" s="70"/>
-      <c r="C11" s="70"/>
-      <c r="D11" s="71"/>
+      <c r="B11" s="45"/>
+      <c r="C11" s="45"/>
+      <c r="D11" s="46"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A12" s="35" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B12" s="8" t="s">
         <v>15</v>
@@ -5378,7 +5416,7 @@
     </row>
     <row r="13" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A13" s="35" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B13" s="20" t="s">
         <v>49</v>
@@ -5392,7 +5430,7 @@
     </row>
     <row r="14" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A14" s="33" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B14" s="20" t="s">
         <v>49</v>
@@ -5406,7 +5444,7 @@
     </row>
     <row r="15" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A15" s="33" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B15" s="20" t="s">
         <v>49</v>
@@ -5420,7 +5458,7 @@
     </row>
     <row r="16" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A16" s="33" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B16" s="20" t="s">
         <v>29</v>
@@ -5434,7 +5472,7 @@
     </row>
     <row r="17" spans="1:4" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A17" s="33" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B17" s="20" t="s">
         <v>29</v>
@@ -5448,7 +5486,7 @@
     </row>
     <row r="18" spans="1:4" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A18" s="33" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B18" s="20" t="s">
         <v>29</v>
@@ -5462,7 +5500,7 @@
     </row>
     <row r="19" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A19" s="33" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B19" s="20" t="s">
         <v>49</v>
@@ -5476,7 +5514,7 @@
     </row>
     <row r="20" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A20" s="33" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B20" s="20" t="s">
         <v>29</v>
@@ -5490,7 +5528,7 @@
     </row>
     <row r="21" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A21" s="33" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B21" s="20" t="s">
         <v>112</v>
@@ -5504,7 +5542,7 @@
     </row>
     <row r="22" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A22" s="33" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B22" s="20" t="s">
         <v>29</v>
@@ -5518,7 +5556,7 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A23" s="33" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B23" s="20" t="s">
         <v>5</v>
@@ -5532,7 +5570,7 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A24" s="33" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B24" s="20" t="s">
         <v>25</v>
@@ -5546,7 +5584,7 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A25" s="33" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B25" s="20" t="s">
         <v>51</v>
@@ -5560,7 +5598,7 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A26" s="34" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B26" s="8" t="s">
         <v>49</v>
@@ -5574,7 +5612,7 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A27" s="34" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B27" s="8" t="s">
         <v>25</v>
@@ -5588,7 +5626,7 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A28" s="34" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B28" s="8" t="s">
         <v>51</v>
@@ -5625,16 +5663,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A1" s="63" t="s">
+      <c r="A1" s="56" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="62"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="55"/>
     </row>
     <row r="2" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B2" s="8" t="s">
         <v>5</v>
@@ -5648,7 +5686,7 @@
     </row>
     <row r="3" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A3" s="19" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>5</v>
@@ -5662,7 +5700,7 @@
     </row>
     <row r="4" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A4" s="19" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>5</v>
@@ -5676,7 +5714,7 @@
     </row>
     <row r="5" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A5" s="19" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>5</v>
@@ -5690,7 +5728,7 @@
     </row>
     <row r="6" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A6" s="19" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>5</v>
@@ -5704,7 +5742,7 @@
     </row>
     <row r="7" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A7" s="19" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B7" s="8" t="s">
         <v>25</v>
@@ -5718,7 +5756,7 @@
     </row>
     <row r="8" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A8" s="19" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B8" s="8" t="s">
         <v>25</v>
@@ -5732,7 +5770,7 @@
     </row>
     <row r="9" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A9" s="19" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B9" s="8" t="s">
         <v>25</v>
@@ -5746,7 +5784,7 @@
     </row>
     <row r="10" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A10" s="19" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>25</v>
@@ -5760,7 +5798,7 @@
     </row>
     <row r="11" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A11" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>15</v>
@@ -5774,7 +5812,7 @@
     </row>
     <row r="12" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A12" s="19" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B12" s="8" t="s">
         <v>9</v>
@@ -5783,12 +5821,12 @@
         <v>10</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A13" s="19" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>49</v>
@@ -5802,7 +5840,7 @@
     </row>
     <row r="14" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A14" s="19" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>51</v>
@@ -5816,7 +5854,7 @@
     </row>
     <row r="15" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A15" s="19" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B15" s="8" t="s">
         <v>29</v>
@@ -5830,7 +5868,7 @@
     </row>
     <row r="16" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A16" s="19" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B16" s="8" t="s">
         <v>5</v>
@@ -5844,7 +5882,7 @@
     </row>
     <row r="17" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A17" s="19" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B17" s="8" t="s">
         <v>5</v>
@@ -5858,7 +5896,7 @@
     </row>
     <row r="18" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A18" s="19" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B18" s="8" t="s">
         <v>5</v>
@@ -5872,7 +5910,7 @@
     </row>
     <row r="19" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A19" s="19" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B19" s="8" t="s">
         <v>9</v>
@@ -5886,7 +5924,7 @@
     </row>
     <row r="20" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A20" s="19" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B20" s="8" t="s">
         <v>9</v>
@@ -5900,7 +5938,7 @@
     </row>
     <row r="21" spans="1:4" s="13" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="19" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B21" s="8" t="s">
         <v>9</v>
@@ -5909,34 +5947,34 @@
         <v>10</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A22" s="25" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B22" s="26" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C22" s="27">
         <v>0</v>
       </c>
       <c r="D22" s="28" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A23" s="60" t="s">
-        <v>134</v>
-      </c>
-      <c r="B23" s="61"/>
-      <c r="C23" s="61"/>
-      <c r="D23" s="62"/>
+      <c r="A23" s="53" t="s">
+        <v>133</v>
+      </c>
+      <c r="B23" s="54"/>
+      <c r="C23" s="54"/>
+      <c r="D23" s="55"/>
     </row>
     <row r="24" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A24" s="19" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B24" s="8" t="s">
         <v>15</v>
@@ -5945,12 +5983,12 @@
         <v>16</v>
       </c>
       <c r="D24" s="29" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A25" s="19" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B25" s="8" t="s">
         <v>15</v>
@@ -5964,7 +6002,7 @@
     </row>
     <row r="26" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A26" s="19" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B26" s="8" t="s">
         <v>15</v>
@@ -5978,7 +6016,7 @@
     </row>
     <row r="27" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A27" s="19" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B27" s="8" t="s">
         <v>15</v>
@@ -5992,7 +6030,7 @@
     </row>
     <row r="28" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A28" s="19" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B28" s="8" t="s">
         <v>25</v>
@@ -6006,7 +6044,7 @@
     </row>
     <row r="29" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A29" s="19" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B29" s="8" t="s">
         <v>25</v>
@@ -6020,7 +6058,7 @@
     </row>
     <row r="30" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A30" s="19" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B30" s="8" t="s">
         <v>25</v>
@@ -6034,7 +6072,7 @@
     </row>
     <row r="31" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A31" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B31" s="8" t="s">
         <v>29</v>
@@ -6048,7 +6086,7 @@
     </row>
     <row r="32" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A32" s="19" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B32" s="8" t="s">
         <v>29</v>
@@ -6062,7 +6100,7 @@
     </row>
     <row r="33" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A33" s="19" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B33" s="8" t="s">
         <v>29</v>
@@ -6096,24 +6134,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A1" s="64" t="s">
-        <v>129</v>
-      </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="66"/>
+      <c r="A1" s="62" t="s">
+        <v>128</v>
+      </c>
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="64"/>
     </row>
     <row r="2" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A2" s="67" t="s">
+      <c r="A2" s="65" t="s">
         <v>59</v>
       </c>
-      <c r="B2" s="65"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="66"/>
+      <c r="B2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="64"/>
     </row>
     <row r="3" spans="1:4" ht="24" x14ac:dyDescent="0.2">
       <c r="A3" s="16" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>15</v>
@@ -6127,7 +6165,7 @@
     </row>
     <row r="4" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A4" s="16" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>15</v>
@@ -6141,7 +6179,7 @@
     </row>
     <row r="5" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A5" s="16" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>25</v>
@@ -6154,16 +6192,16 @@
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A6" s="68" t="s">
-        <v>246</v>
-      </c>
-      <c r="B6" s="65"/>
-      <c r="C6" s="65"/>
-      <c r="D6" s="66"/>
+      <c r="A6" s="66" t="s">
+        <v>245</v>
+      </c>
+      <c r="B6" s="63"/>
+      <c r="C6" s="63"/>
+      <c r="D6" s="64"/>
     </row>
     <row r="7" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A7" s="16" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B7" s="17" t="s">
         <v>15</v>
@@ -6177,7 +6215,7 @@
     </row>
     <row r="8" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A8" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B8" s="17" t="s">
         <v>5</v>
@@ -6191,7 +6229,7 @@
     </row>
     <row r="9" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A9" s="16" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B9" s="17" t="s">
         <v>5</v>
@@ -6205,7 +6243,7 @@
     </row>
     <row r="10" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A10" s="16" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B10" s="17" t="s">
         <v>5</v>
@@ -6219,7 +6257,7 @@
     </row>
     <row r="11" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A11" s="16" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B11" s="17" t="s">
         <v>5</v>
@@ -6233,7 +6271,7 @@
     </row>
     <row r="12" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A12" s="16" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>9</v>
@@ -6247,7 +6285,7 @@
     </row>
     <row r="13" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A13" s="16" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>9</v>
@@ -6261,7 +6299,7 @@
     </row>
     <row r="14" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A14" s="16" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>5</v>
@@ -6275,7 +6313,7 @@
     </row>
     <row r="15" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A15" s="16" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B15" s="17" t="s">
         <v>49</v>
@@ -6284,12 +6322,12 @@
         <v>21</v>
       </c>
       <c r="D15" s="23" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A16" s="16" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B16" s="17" t="s">
         <v>49</v>
@@ -6298,12 +6336,12 @@
         <v>21</v>
       </c>
       <c r="D16" s="23" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A17" s="16" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B17" s="17" t="s">
         <v>49</v>
@@ -6312,7 +6350,7 @@
         <v>21</v>
       </c>
       <c r="D17" s="23" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
@@ -6328,16 +6366,16 @@
       <c r="D20" s="3"/>
     </row>
     <row r="21" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A21" s="68" t="s">
-        <v>245</v>
-      </c>
-      <c r="B21" s="79"/>
-      <c r="C21" s="79"/>
-      <c r="D21" s="80"/>
+      <c r="A21" s="66" t="s">
+        <v>244</v>
+      </c>
+      <c r="B21" s="68"/>
+      <c r="C21" s="68"/>
+      <c r="D21" s="69"/>
     </row>
     <row r="22" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A22" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B22" s="17" t="s">
         <v>5</v>
@@ -6351,7 +6389,7 @@
     </row>
     <row r="23" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A23" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B23" s="17" t="s">
         <v>5</v>
@@ -6365,7 +6403,7 @@
     </row>
     <row r="24" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A24" s="16" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B24" s="17" t="s">
         <v>25</v>
@@ -6379,7 +6417,7 @@
     </row>
     <row r="25" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A25" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B25" s="17" t="s">
         <v>49</v>
@@ -6388,26 +6426,26 @@
         <v>21</v>
       </c>
       <c r="D25" s="30" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A26" s="16" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B26" s="17" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C26" s="17" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="30" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A27" s="16" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B27" s="17" t="s">
         <v>5</v>
@@ -6421,7 +6459,7 @@
     </row>
     <row r="28" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A28" s="16" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>5</v>
@@ -6435,7 +6473,7 @@
     </row>
     <row r="29" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A29" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>5</v>
@@ -6449,7 +6487,7 @@
     </row>
     <row r="30" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A30" s="16" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>9</v>
@@ -6463,7 +6501,7 @@
     </row>
     <row r="31" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A31" s="16" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>9</v>
@@ -6477,7 +6515,7 @@
     </row>
     <row r="32" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A32" s="16" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>9</v>
@@ -6491,7 +6529,7 @@
     </row>
     <row r="33" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A33" s="16" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>9</v>
@@ -6500,12 +6538,12 @@
         <v>10</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A34" s="16" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>15</v>
@@ -6519,21 +6557,21 @@
     </row>
     <row r="35" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A35" s="16" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D35" s="30" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="24" x14ac:dyDescent="0.2">
       <c r="A36" s="16" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>13</v>
@@ -6547,7 +6585,7 @@
     </row>
     <row r="37" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A37" s="16" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>15</v>
@@ -6560,16 +6598,16 @@
       </c>
     </row>
     <row r="38" spans="1:4" ht="15" x14ac:dyDescent="0.25">
-      <c r="A38" s="68" t="s">
-        <v>254</v>
-      </c>
-      <c r="B38" s="65"/>
-      <c r="C38" s="65"/>
-      <c r="D38" s="66"/>
+      <c r="A38" s="66" t="s">
+        <v>253</v>
+      </c>
+      <c r="B38" s="63"/>
+      <c r="C38" s="63"/>
+      <c r="D38" s="64"/>
     </row>
     <row r="39" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A39" s="16" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B39" s="17" t="s">
         <v>15</v>
@@ -6583,7 +6621,7 @@
     </row>
     <row r="40" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A40" s="16" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B40" s="17" t="s">
         <v>15</v>
@@ -6597,7 +6635,7 @@
     </row>
     <row r="41" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A41" s="16" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B41" s="17" t="s">
         <v>15</v>
@@ -6611,7 +6649,7 @@
     </row>
     <row r="42" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A42" s="16" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B42" s="17" t="s">
         <v>15</v>
@@ -6625,7 +6663,7 @@
     </row>
     <row r="43" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A43" s="16" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B43" s="17" t="s">
         <v>25</v>
@@ -6639,7 +6677,7 @@
     </row>
     <row r="44" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A44" s="16" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>25</v>
@@ -6653,7 +6691,7 @@
     </row>
     <row r="45" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A45" s="16" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>25</v>
